--- a/assets_management/tests/data/account_invoice_line.xlsx
+++ b/assets_management/tests/data/account_invoice_line.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -94,6 +94,21 @@
     <t xml:space="preserve">Asset Three</t>
   </si>
   <si>
+    <t xml:space="preserve">z0bug.sale_invoice_4_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Four (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">525.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.tax_22v</t>
+  </si>
+  <si>
     <t xml:space="preserve">z0bug.sale_invoice_1_1</t>
   </si>
   <si>
@@ -101,9 +116,6 @@
   </si>
   <si>
     <t xml:space="preserve">1400.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.tax_22v</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.sale_invoice_1_2</t>
@@ -337,7 +349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:XFD8"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.49"/>
@@ -491,43 +503,74 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="XEY6" s="0"/>
+      <c r="XEZ6" s="0"/>
+      <c r="XFA6" s="0"/>
+      <c r="XFB6" s="0"/>
+      <c r="XFC6" s="0"/>
+      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
     </row>

--- a/assets_management/tests/data/account_invoice_line.xlsx
+++ b/assets_management/tests/data/account_invoice_line.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -109,19 +109,25 @@
     <t xml:space="preserve">z0bug.tax_22v</t>
   </si>
   <si>
-    <t xml:space="preserve">z0bug.sale_invoice_1_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.sale_invoice_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1400.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.sale_invoice_1_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3210.0</t>
+    <t xml:space="preserve">z0bug.sale_invoice_2_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_13_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_13_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.0</t>
   </si>
 </sst>
 </file>
@@ -349,7 +355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD8"/>
+  <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.49"/>
@@ -517,12 +523,6 @@
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="XEY6" s="0"/>
-      <c r="XEZ6" s="0"/>
-      <c r="XFA6" s="0"/>
-      <c r="XFB6" s="0"/>
-      <c r="XFC6" s="0"/>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -534,13 +534,13 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>28</v>
@@ -551,15 +551,15 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>12</v>
@@ -573,7 +573,45 @@
       <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
+      <c r="XEY8" s="0"/>
+      <c r="XEZ8" s="0"/>
+      <c r="XFA8" s="0"/>
+      <c r="XFB8" s="0"/>
+      <c r="XFC8" s="0"/>
+      <c r="XFD8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="XEY9" s="0"/>
+      <c r="XEZ9" s="0"/>
+      <c r="XFA9" s="0"/>
+      <c r="XFB9" s="0"/>
+      <c r="XFC9" s="0"/>
+      <c r="XFD9" s="0"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
